--- a/Data Files/Mission_Config_Example.xlsx
+++ b/Data Files/Mission_Config_Example.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/20cdd465efad1a15/Desktop/CubeSatMissionPlanner/Data Files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sebas\OneDrive\Desktop\CubeSatMissionPlanner\Data Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{5444EFF1-4C62-49BC-817B-78941E2EB9BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90929F21-F33E-4A23-8B38-D01B7316B57E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E524B73-DA96-4507-8D61-F90C82D39E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="413" yWindow="1477" windowWidth="21187" windowHeight="12023" firstSheet="4" activeTab="4" xr2:uid="{103AC5D8-21F7-4928-8616-0E1C76F0EB80}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" firstSheet="4" activeTab="7" xr2:uid="{103AC5D8-21F7-4928-8616-0E1C76F0EB80}"/>
   </bookViews>
   <sheets>
     <sheet name="Targets_Info" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="88">
   <si>
     <t>G191B2B</t>
   </si>
@@ -299,6 +299,15 @@
   <si>
     <t>Simulation End Time [YYYY-MM-DD HH:MM:SS UTC]</t>
   </si>
+  <si>
+    <t>ICA</t>
+  </si>
+  <si>
+    <t>Earth Angle Constraint</t>
+  </si>
+  <si>
+    <t>Moon Angle Constraint</t>
+  </si>
 </sst>
 </file>
 
@@ -398,7 +407,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -460,6 +469,7 @@
     <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7816,10 +7826,10 @@
         <v>72</v>
       </c>
       <c r="D2" s="24">
-        <v>45427</v>
+        <v>45306</v>
       </c>
       <c r="E2" s="24">
-        <v>45427.5</v>
+        <v>45307</v>
       </c>
       <c r="F2" s="23">
         <v>6</v>
@@ -7833,7 +7843,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E0C19B4-3755-45CE-8EA4-F53B71398157}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="23.59765625" defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="16384" width="23.59765625" style="21"/>
@@ -7875,6 +7885,23 @@
       </c>
       <c r="F2" s="25"/>
     </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="21">
+        <v>28.476061000000001</v>
+      </c>
+      <c r="C3" s="21">
+        <v>-16.307661</v>
+      </c>
+      <c r="D3" s="21">
+        <v>475</v>
+      </c>
+      <c r="E3" s="21">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7883,7 +7910,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46B729A2-E962-4215-99F7-898E63B790C1}">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B101"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
@@ -7898,160 +7925,800 @@
       <c r="A2">
         <v>-20</v>
       </c>
-      <c r="B2">
-        <v>0</v>
+      <c r="B2" s="27">
+        <v>6.5900000000000002E-15</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3">
-        <v>-25</v>
+        <v>-20.959595960000001</v>
       </c>
       <c r="B3">
-        <v>15</v>
+        <v>2.8787878789999999</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4">
-        <v>-30</v>
+        <v>-21.919191919999999</v>
       </c>
       <c r="B4">
-        <v>30</v>
+        <v>5.7575757579999998</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5">
-        <v>-35</v>
+        <v>-22.878787880000001</v>
       </c>
       <c r="B5">
-        <v>35</v>
+        <v>8.6363636360000005</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6">
-        <v>-38</v>
+        <v>-23.838383839999999</v>
       </c>
       <c r="B6">
-        <v>30</v>
+        <v>11.51515152</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7">
-        <v>-40</v>
+        <v>-24.7979798</v>
       </c>
       <c r="B7">
-        <v>15</v>
+        <v>14.39393939</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A8">
-        <v>-45</v>
+        <v>-25.757575760000002</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>17.36596737</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9">
-        <v>-53</v>
+        <v>-26.71717172</v>
       </c>
       <c r="B9">
-        <v>-15</v>
+        <v>20.382496289999999</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10">
-        <v>-60</v>
+        <v>-27.676767680000001</v>
       </c>
       <c r="B10">
-        <v>-30</v>
+        <v>23.26811236</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11">
-        <v>-60</v>
+        <v>-28.636363639999999</v>
       </c>
       <c r="B11">
-        <v>-45</v>
+        <v>25.892138159999998</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A12">
-        <v>-50</v>
+        <v>-29.5959596</v>
       </c>
       <c r="B12">
-        <v>-60</v>
+        <v>28.168632710000001</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A13">
-        <v>-40</v>
+        <v>-30.567422480000001</v>
       </c>
       <c r="B13">
-        <v>-75</v>
+        <v>30.11572602</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A14">
-        <v>-27</v>
+        <v>-31.556261920000001</v>
       </c>
       <c r="B14">
-        <v>-80</v>
+        <v>31.76449813</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A15">
-        <v>-22</v>
+        <v>-32.525511530000003</v>
       </c>
       <c r="B15">
-        <v>-80</v>
+        <v>32.978385250000002</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A16">
-        <v>-15</v>
+        <v>-33.447152170000003</v>
       </c>
       <c r="B16">
-        <v>-75</v>
+        <v>33.71029644</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17">
-        <v>-7</v>
+        <v>-34.302112030000004</v>
       </c>
       <c r="B17">
-        <v>-60</v>
+        <v>34.00261355</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A18">
-        <v>-5</v>
+        <v>-35.082809449999999</v>
       </c>
       <c r="B18">
-        <v>-45</v>
+        <v>34.012620380000001</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19">
-        <v>-7</v>
+        <v>-35.798450709999997</v>
       </c>
       <c r="B19">
-        <v>-30</v>
+        <v>33.829789740000002</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A20">
-        <v>-12</v>
+        <v>-36.4373808</v>
       </c>
       <c r="B20">
-        <v>-15</v>
+        <v>33.2309105</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21">
-        <v>-20</v>
+        <v>-37.001365640000003</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>32.150055330000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A22">
+        <v>-37.505592049999997</v>
+      </c>
+      <c r="B22">
+        <v>30.610769699999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A23">
+        <v>-37.978667799999997</v>
+      </c>
+      <c r="B23">
+        <v>28.726071910000002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A24">
+        <v>-38.386852210000001</v>
+      </c>
+      <c r="B24">
+        <v>26.548468369999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A25">
+        <v>-38.767417770000002</v>
+      </c>
+      <c r="B25">
+        <v>24.005674460000002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A26">
+        <v>-39.175460899999997</v>
+      </c>
+      <c r="B26">
+        <v>21.171858440000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A27">
+        <v>-39.65713075</v>
+      </c>
+      <c r="B27">
+        <v>18.16592498</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A28">
+        <v>-40.249629159999998</v>
+      </c>
+      <c r="B28">
+        <v>15.15151515</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A29">
+        <v>-40.939182029999998</v>
+      </c>
+      <c r="B29">
+        <v>12.272727270000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A30">
+        <v>-41.738009470000001</v>
+      </c>
+      <c r="B30">
+        <v>9.3939393940000002</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A31">
+        <v>-42.677191499999999</v>
+      </c>
+      <c r="B31">
+        <v>6.5151515150000003</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A32">
+        <v>-43.760966310000001</v>
+      </c>
+      <c r="B32">
+        <v>3.636363636</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A33">
+        <v>-44.966730239999997</v>
+      </c>
+      <c r="B33">
+        <v>0.75757575799999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A34">
+        <v>-46.253514160000002</v>
+      </c>
+      <c r="B34">
+        <v>-2.1212121210000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A35">
+        <v>-47.657766479999999</v>
+      </c>
+      <c r="B35">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A36">
+        <v>-49.147653689999999</v>
+      </c>
+      <c r="B36">
+        <v>-7.8787878789999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A37">
+        <v>-50.67985213</v>
+      </c>
+      <c r="B37">
+        <v>-10.75757576</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A38">
+        <v>-52.202090839999997</v>
+      </c>
+      <c r="B38">
+        <v>-13.636363640000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A39">
+        <v>-53.68875233</v>
+      </c>
+      <c r="B39">
+        <v>-16.51515152</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A40">
+        <v>-55.192295919999999</v>
+      </c>
+      <c r="B40">
+        <v>-19.39393939</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A41">
+        <v>-56.598996960000001</v>
+      </c>
+      <c r="B41">
+        <v>-22.272727270000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A42">
+        <v>-57.81820536</v>
+      </c>
+      <c r="B42">
+        <v>-25.151515150000002</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A43">
+        <v>-58.795060159999998</v>
+      </c>
+      <c r="B43">
+        <v>-28.030303029999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A44">
+        <v>-59.52744225</v>
+      </c>
+      <c r="B44">
+        <v>-30.90909091</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A45">
+        <v>-60.133549950000003</v>
+      </c>
+      <c r="B45">
+        <v>-33.787878790000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A46">
+        <v>-60.434696619999997</v>
+      </c>
+      <c r="B46">
+        <v>-36.666666669999998</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A47">
+        <v>-60.335876239999997</v>
+      </c>
+      <c r="B47">
+        <v>-39.545454550000002</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A48">
+        <v>-59.818134729999997</v>
+      </c>
+      <c r="B48">
+        <v>-42.424242419999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A49">
+        <v>-58.93856985</v>
+      </c>
+      <c r="B49">
+        <v>-45.303030300000003</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A50">
+        <v>-57.74034047</v>
+      </c>
+      <c r="B50">
+        <v>-48.18181818</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A51">
+        <v>-56.173388899999999</v>
+      </c>
+      <c r="B51">
+        <v>-51.060606059999998</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A52">
+        <v>-54.30952885</v>
+      </c>
+      <c r="B52">
+        <v>-53.939393940000002</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A53">
+        <v>-52.265310450000001</v>
+      </c>
+      <c r="B53">
+        <v>-56.81818182</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A54">
+        <v>-50.2020202</v>
+      </c>
+      <c r="B54">
+        <v>-59.696969699999997</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A55">
+        <v>-48.315886130000003</v>
+      </c>
+      <c r="B55">
+        <v>-62.685950409999997</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A56">
+        <v>-46.436745070000001</v>
+      </c>
+      <c r="B56">
+        <v>-65.698241150000001</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A57">
+        <v>-44.513385599999999</v>
+      </c>
+      <c r="B57">
+        <v>-68.5631372</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A58">
+        <v>-42.508017240000001</v>
+      </c>
+      <c r="B58">
+        <v>-71.154670249999995</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A59">
+        <v>-40.396270399999999</v>
+      </c>
+      <c r="B59">
+        <v>-73.391608390000002</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A60">
+        <v>-38.106166559999998</v>
+      </c>
+      <c r="B60">
+        <v>-75.275599819999996</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A61">
+        <v>-35.648654380000004</v>
+      </c>
+      <c r="B61">
+        <v>-76.809587719999996</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A62">
+        <v>-33.183725369999998</v>
+      </c>
+      <c r="B62">
+        <v>-77.956487960000004</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A63">
+        <v>-30.849002850000002</v>
+      </c>
+      <c r="B63">
+        <v>-78.746321019999996</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A64">
+        <v>-28.759741940000001</v>
+      </c>
+      <c r="B64">
+        <v>-79.276212000000001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A65">
+        <v>-27.017305929999999</v>
+      </c>
+      <c r="B65">
+        <v>-79.731581550000001</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A66">
+        <v>-25.621788989999999</v>
+      </c>
+      <c r="B66">
+        <v>-80.098066919999994</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A67">
+        <v>-24.48517812</v>
+      </c>
+      <c r="B67">
+        <v>-80.251818889999996</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A68">
+        <v>-23.50787596</v>
+      </c>
+      <c r="B68">
+        <v>-80.164582890000005</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A69">
+        <v>-22.563443289999999</v>
+      </c>
+      <c r="B69">
+        <v>-79.852840760000007</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A70">
+        <v>-21.499446679999998</v>
+      </c>
+      <c r="B70">
+        <v>-79.386287109999998</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A71">
+        <v>-20.304231120000001</v>
+      </c>
+      <c r="B71">
+        <v>-78.916437099999996</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A72">
+        <v>-19.032539849999999</v>
+      </c>
+      <c r="B72">
+        <v>-78.219020040000004</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A73">
+        <v>-17.684726049999998</v>
+      </c>
+      <c r="B73">
+        <v>-77.179251719999996</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A74">
+        <v>-16.274563820000001</v>
+      </c>
+      <c r="B74">
+        <v>-75.749452570000003</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A75">
+        <v>-14.829248189999999</v>
+      </c>
+      <c r="B75">
+        <v>-73.949047590000006</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A76">
+        <v>-13.28659556</v>
+      </c>
+      <c r="B76">
+        <v>-71.811000449999995</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A77">
+        <v>-11.71180335</v>
+      </c>
+      <c r="B77">
+        <v>-69.300699300000005</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A78">
+        <v>-10.21000212</v>
+      </c>
+      <c r="B78">
+        <v>-66.487603309999997</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A79">
+        <v>-8.8639542280000008</v>
+      </c>
+      <c r="B79">
+        <v>-63.485908029999997</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A80">
+        <v>-7.7340538250000002</v>
+      </c>
+      <c r="B80">
+        <v>-60.454545449999998</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A81">
+        <v>-6.8154976339999997</v>
+      </c>
+      <c r="B81">
+        <v>-57.575757580000001</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A82">
+        <v>-6.1109698379999999</v>
+      </c>
+      <c r="B82">
+        <v>-54.696969699999997</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A83">
+        <v>-5.6536695630000002</v>
+      </c>
+      <c r="B83">
+        <v>-51.81818182</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A84">
+        <v>-5.4320595230000004</v>
+      </c>
+      <c r="B84">
+        <v>-48.939393940000002</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A85">
+        <v>-5.389866026</v>
+      </c>
+      <c r="B85">
+        <v>-46.060606059999998</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A86">
+        <v>-5.4057356780000001</v>
+      </c>
+      <c r="B86">
+        <v>-43.18181818</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A87">
+        <v>-5.5370723550000003</v>
+      </c>
+      <c r="B87">
+        <v>-40.303030300000003</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A88">
+        <v>-5.8336276519999997</v>
+      </c>
+      <c r="B88">
+        <v>-37.424242419999999</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A89">
+        <v>-6.2985802079999997</v>
+      </c>
+      <c r="B89">
+        <v>-34.545454550000002</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A90">
+        <v>-6.9037931769999998</v>
+      </c>
+      <c r="B90">
+        <v>-31.666666670000001</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A91">
+        <v>-7.5796425799999998</v>
+      </c>
+      <c r="B91">
+        <v>-28.787878790000001</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A92">
+        <v>-8.312778131</v>
+      </c>
+      <c r="B92">
+        <v>-25.90909091</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A93">
+        <v>-9.1721409900000008</v>
+      </c>
+      <c r="B93">
+        <v>-23.030303029999999</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A94">
+        <v>-10.17609663</v>
+      </c>
+      <c r="B94">
+        <v>-20.151515150000002</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A95">
+        <v>-11.316168680000001</v>
+      </c>
+      <c r="B95">
+        <v>-17.272727270000001</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A96">
+        <v>-12.55703892</v>
+      </c>
+      <c r="B96">
+        <v>-14.39393939</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A97">
+        <v>-13.87066469</v>
+      </c>
+      <c r="B97">
+        <v>-11.51515152</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A98">
+        <v>-15.28353465</v>
+      </c>
+      <c r="B98">
+        <v>-8.6363636360000005</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A99">
+        <v>-16.795648799999999</v>
+      </c>
+      <c r="B99">
+        <v>-5.7575757579999998</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A100">
+        <v>-18.40700713</v>
+      </c>
+      <c r="B100">
+        <v>-2.8787878789999999</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A101">
+        <v>-20.117609659999999</v>
+      </c>
+      <c r="B101" s="27">
+        <v>-1.7800000000000001E-14</v>
       </c>
     </row>
   </sheetData>
@@ -8061,16 +8728,28 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE6D1A22-A2FA-4596-A1F2-C276965E6ED6}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="B1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2">
+        <v>15</v>
+      </c>
+      <c r="B2">
+        <v>15</v>
+      </c>
+      <c r="C2">
         <v>15</v>
       </c>
     </row>
